--- a/AAII_Financials/Quarterly/TYGO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TYGO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="92">
   <si>
     <t>TYGO</t>
   </si>
@@ -656,301 +656,314 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>25400</v>
+      </c>
+      <c r="E8" s="3">
         <v>25200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>30000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>30600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>24100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>18800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>17300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>14200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>12700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>9800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>9200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>17100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>68800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>50100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>30900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>22800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>17600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>9900</v>
       </c>
-      <c r="U8" s="3">
-        <v>0</v>
-      </c>
       <c r="V8" s="3">
         <v>0</v>
       </c>
       <c r="W8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>15400</v>
+      </c>
+      <c r="E9" s="3">
         <v>14400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>16700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>17600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>13300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>11700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>29800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>12500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>8800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>7000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>6400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>12900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>42900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>31700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>21000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>16200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>12100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>7200</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V9" s="3" t="s">
         <v>4</v>
       </c>
       <c r="W9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E10" s="3">
         <v>10800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>13400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>13100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>10800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>7200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-12600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>4200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>25900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>18400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>9900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>6600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>5500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2700</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V10" s="3" t="s">
         <v>4</v>
       </c>
       <c r="W10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -974,40 +987,41 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E12" s="3">
         <v>2600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>2300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>2500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>2300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>2200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>2300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>2400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>2700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>2500</v>
-      </c>
-      <c r="M12" s="3">
-        <v>2400</v>
       </c>
       <c r="N12" s="3">
         <v>2400</v>
@@ -1016,22 +1030,22 @@
         <v>2400</v>
       </c>
       <c r="P12" s="3">
+        <v>2400</v>
+      </c>
+      <c r="Q12" s="3">
         <v>2200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>1200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>1600</v>
-      </c>
-      <c r="S12" s="3">
-        <v>1400</v>
       </c>
       <c r="T12" s="3">
         <v>1400</v>
       </c>
-      <c r="U12" s="3" t="s">
-        <v>4</v>
+      <c r="U12" s="3">
+        <v>1400</v>
       </c>
       <c r="V12" s="3" t="s">
         <v>4</v>
@@ -1039,8 +1053,11 @@
       <c r="W12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1104,20 +1121,23 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E14" s="3">
+      <c r="D14" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="3">
         <v>-13500</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1136,21 +1156,21 @@
       <c r="L14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N14" s="3">
         <v>-400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-3000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>3200</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>4400</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
@@ -1158,24 +1178,27 @@
         <v>0</v>
       </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>3600</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
       <c r="V14" s="3">
         <v>0</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="E15" s="3">
         <v>300</v>
@@ -1187,10 +1210,10 @@
         <v>300</v>
       </c>
       <c r="H15" s="3">
+        <v>300</v>
+      </c>
+      <c r="I15" s="3">
         <v>400</v>
-      </c>
-      <c r="I15" s="3">
-        <v>300</v>
       </c>
       <c r="J15" s="3">
         <v>300</v>
@@ -1211,13 +1234,13 @@
         <v>300</v>
       </c>
       <c r="P15" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q15" s="3">
         <v>200</v>
       </c>
-      <c r="Q15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R15" s="3">
-        <v>0</v>
+      <c r="R15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S15" s="3">
         <v>0</v>
@@ -1234,8 +1257,11 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1256,138 +1282,145 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>27100</v>
+      </c>
+      <c r="E17" s="3">
         <v>27600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>29700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>30000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>25600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>22800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>41400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>24700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>21100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>18900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>22800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>28300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>60200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>38200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>28800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>24900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>17000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>15100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>100</v>
       </c>
-      <c r="W17" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E18" s="3">
         <v>-2400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-4000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-24100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-10400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-8400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-9100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-13500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-11200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>8700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>11900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-2100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-5200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-100</v>
       </c>
-      <c r="W18" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1411,138 +1444,145 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E20" s="3">
         <v>-500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-300</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-100</v>
       </c>
       <c r="H20" s="3">
         <v>-100</v>
       </c>
       <c r="I20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J20" s="3">
         <v>600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-200</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>-400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-51100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>37000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-500</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
         <v>0</v>
       </c>
       <c r="W20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-1600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-1100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-3500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-24400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-10000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-8100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-8400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-14200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>40200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-28000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>12400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-2200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-5600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-100</v>
       </c>
-      <c r="W21" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1550,10 +1590,10 @@
         <v>0</v>
       </c>
       <c r="E22" s="3">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3">
         <v>2400</v>
-      </c>
-      <c r="F22" s="3">
-        <v>2900</v>
       </c>
       <c r="G22" s="3">
         <v>2900</v>
@@ -1571,23 +1611,23 @@
         <v>2900</v>
       </c>
       <c r="L22" s="3">
+        <v>2900</v>
+      </c>
+      <c r="M22" s="3">
         <v>2800</v>
-      </c>
-      <c r="M22" s="3">
-        <v>2900</v>
       </c>
       <c r="N22" s="3">
         <v>2900</v>
       </c>
       <c r="O22" s="3">
+        <v>2900</v>
+      </c>
+      <c r="P22" s="3">
         <v>1600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>800</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
       <c r="R22" s="3">
         <v>0</v>
       </c>
@@ -1606,126 +1646,132 @@
       <c r="W22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>11600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-4300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-6700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-26700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-13100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-11300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-11500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-14700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>40000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-33100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>6900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-2400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-5700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-100</v>
       </c>
-      <c r="W23" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E24" s="3">
         <v>-200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-100</v>
-      </c>
-      <c r="F24" s="3">
-        <v>200</v>
       </c>
       <c r="G24" s="3">
         <v>200</v>
       </c>
       <c r="H24" s="3">
+        <v>200</v>
+      </c>
+      <c r="I24" s="3">
         <v>300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>100</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
-      <c r="L24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M24" s="3">
+      <c r="K24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N24" s="3">
         <v>100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>11000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-10900</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
       <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
         <v>100</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
       <c r="S24" s="3">
         <v>0</v>
       </c>
-      <c r="T24" s="3" t="s">
-        <v>4</v>
+      <c r="T24" s="3">
+        <v>0</v>
       </c>
       <c r="U24" s="3" t="s">
         <v>4</v>
@@ -1736,8 +1782,11 @@
       <c r="W24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1801,138 +1850,147 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>11700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-2200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-4400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-7000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-26800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-13100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-11300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-11500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-14800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>29100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-22200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>6900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-2400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-5700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-100</v>
       </c>
-      <c r="W26" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>11700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-2200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-4400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-7000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-26800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-13100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-11300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-11500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-8800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>29100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-28000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>4800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-1200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-4500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-1200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-6500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-100</v>
       </c>
-      <c r="W27" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1996,8 +2054,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2061,8 +2122,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2126,8 +2190,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2191,138 +2258,147 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>300</v>
+      </c>
+      <c r="E32" s="3">
         <v>500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>300</v>
-      </c>
-      <c r="G32" s="3">
-        <v>100</v>
       </c>
       <c r="H32" s="3">
         <v>100</v>
       </c>
       <c r="I32" s="3">
+        <v>100</v>
+      </c>
+      <c r="J32" s="3">
         <v>-600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>200</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>51100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-37000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>500</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
         <v>0</v>
       </c>
       <c r="W32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>11700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-2200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-4400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-7000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-26800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-13100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-11300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-11500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-14800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>29100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-22200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>6900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-1200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-4500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-1200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-6500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-100</v>
       </c>
-      <c r="W33" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2386,143 +2462,152 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>11700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-2200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-4400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-7000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-26800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-13100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-11300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-11500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-14800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>29100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-22200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>6900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-1200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-4500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-1200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-6500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-100</v>
       </c>
-      <c r="W35" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2546,8 +2631,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2571,53 +2657,54 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>16900</v>
+      </c>
+      <c r="E41" s="3">
         <v>11600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>7700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>24500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>10200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>8500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>11700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>9500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>14900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>9000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>4400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>11700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>50600</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>4</v>
       </c>
@@ -2627,17 +2714,20 @@
       <c r="T41" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U41" s="3">
+      <c r="U41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V41" s="3">
         <v>800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2648,41 +2738,41 @@
         <v>0</v>
       </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
         <v>15800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>17800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>11800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>8200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>10000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>5200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>12900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>26800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>34400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>43900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>5400</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R42" s="3" t="s">
         <v>4</v>
       </c>
@@ -2692,8 +2782,8 @@
       <c r="T42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U42" s="3">
-        <v>0</v>
+      <c r="U42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V42" s="3">
         <v>0</v>
@@ -2701,53 +2791,56 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>13600</v>
+      </c>
+      <c r="E43" s="3">
         <v>14200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>13900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>15800</v>
-      </c>
-      <c r="G43" s="3">
-        <v>10400</v>
       </c>
       <c r="H43" s="3">
         <v>10400</v>
       </c>
       <c r="I43" s="3">
+        <v>10400</v>
+      </c>
+      <c r="J43" s="3">
         <v>8000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>8800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>6900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>6300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>6900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>20400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>45800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>32400</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R43" s="3" t="s">
         <v>4</v>
       </c>
@@ -2760,59 +2853,62 @@
       <c r="U43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V43" s="3">
-        <v>0</v>
+      <c r="V43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>20600</v>
+      </c>
+      <c r="E44" s="3">
         <v>24800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>31300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>28500</v>
-      </c>
-      <c r="G44" s="3">
-        <v>18900</v>
       </c>
       <c r="H44" s="3">
         <v>18900</v>
       </c>
       <c r="I44" s="3">
+        <v>18900</v>
+      </c>
+      <c r="J44" s="3">
         <v>22000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>46800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>51300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>55800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>61400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>57400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>50600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>36600</v>
       </c>
-      <c r="Q44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R44" s="3" t="s">
         <v>4</v>
       </c>
@@ -2825,14 +2921,17 @@
       <c r="U44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V44" s="3">
-        <v>0</v>
+      <c r="V44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2872,12 +2971,12 @@
       <c r="O45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q45" s="3">
         <v>2700</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R45" s="3" t="s">
         <v>4</v>
       </c>
@@ -2887,62 +2986,65 @@
       <c r="T45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U45" s="3">
+      <c r="U45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V45" s="3">
         <v>200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>54600</v>
+      </c>
+      <c r="E46" s="3">
         <v>55100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>58000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>87800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>60400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>51800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>53400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>78700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>83100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>88400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>104700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>117300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>155900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>132700</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R46" s="3" t="s">
         <v>4</v>
       </c>
@@ -2952,17 +3054,20 @@
       <c r="T46" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U46" s="3">
+      <c r="U46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V46" s="3">
         <v>1000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2993,21 +3098,21 @@
       <c r="L47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M47" s="3">
+      <c r="M47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N47" s="3">
         <v>2000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>4300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>6300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>4700</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R47" s="3" t="s">
         <v>4</v>
       </c>
@@ -3017,62 +3122,65 @@
       <c r="T47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U47" s="3">
-        <v>116700</v>
+      <c r="U47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V47" s="3">
         <v>116700</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="W47" s="3">
+        <v>116700</v>
+      </c>
+      <c r="X47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E48" s="3">
         <v>4700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>5000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>5100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>5200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>6000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>4900</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>4</v>
       </c>
@@ -3082,8 +3190,8 @@
       <c r="T48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U48" s="3">
-        <v>0</v>
+      <c r="U48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V48" s="3">
         <v>0</v>
@@ -3091,53 +3199,56 @@
       <c r="W48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>13700</v>
+      </c>
+      <c r="E49" s="3">
         <v>13800</v>
-      </c>
-      <c r="E49" s="3">
-        <v>13900</v>
       </c>
       <c r="F49" s="3">
         <v>13900</v>
       </c>
       <c r="G49" s="3">
+        <v>13900</v>
+      </c>
+      <c r="H49" s="3">
         <v>14000</v>
-      </c>
-      <c r="H49" s="3">
-        <v>14100</v>
       </c>
       <c r="I49" s="3">
         <v>14100</v>
       </c>
       <c r="J49" s="3">
+        <v>14100</v>
+      </c>
+      <c r="K49" s="3">
         <v>14200</v>
-      </c>
-      <c r="K49" s="3">
-        <v>14300</v>
       </c>
       <c r="L49" s="3">
         <v>14300</v>
       </c>
       <c r="M49" s="3">
+        <v>14300</v>
+      </c>
+      <c r="N49" s="3">
         <v>14400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>15300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>13700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>12600</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R49" s="3" t="s">
         <v>4</v>
       </c>
@@ -3147,8 +3258,8 @@
       <c r="T49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U49" s="3">
-        <v>0</v>
+      <c r="U49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V49" s="3">
         <v>0</v>
@@ -3156,8 +3267,11 @@
       <c r="W49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3221,8 +3335,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3286,37 +3403,40 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="E52" s="3">
         <v>1200</v>
       </c>
       <c r="F52" s="3">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="G52" s="3">
         <v>1100</v>
       </c>
       <c r="H52" s="3">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="I52" s="3">
         <v>1000</v>
       </c>
       <c r="J52" s="3">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="K52" s="3">
         <v>800</v>
       </c>
       <c r="L52" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="M52" s="3">
         <v>700</v>
@@ -3328,11 +3448,11 @@
         <v>700</v>
       </c>
       <c r="P52" s="3">
+        <v>700</v>
+      </c>
+      <c r="Q52" s="3">
         <v>100</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R52" s="3" t="s">
         <v>4</v>
       </c>
@@ -3342,17 +3462,20 @@
       <c r="T52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U52" s="3">
+      <c r="U52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V52" s="3">
         <v>100</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3416,53 +3539,56 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>77900</v>
+      </c>
+      <c r="E54" s="3">
         <v>74900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>78000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>107800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>80600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>70600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>72900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>98600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>103300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>109100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>127800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>143100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>195100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>156900</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>4</v>
       </c>
@@ -3472,17 +3598,20 @@
       <c r="T54" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U54" s="3">
+      <c r="U54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V54" s="3">
         <v>117800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>117900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3506,8 +3635,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3531,53 +3661,54 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>11300</v>
+      </c>
+      <c r="E57" s="3">
         <v>14100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>29200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>28400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>14200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>8000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>8100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>11800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>7100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>6000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>15700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>19500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>54100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>39700</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>4</v>
       </c>
@@ -3587,17 +3718,20 @@
       <c r="T57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U57" s="3">
+      <c r="U57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V57" s="3">
         <v>200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>100</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3608,41 +3742,41 @@
         <v>900</v>
       </c>
       <c r="F58" s="3">
+        <v>900</v>
+      </c>
+      <c r="G58" s="3">
         <v>48000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>45700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>43200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1100</v>
-      </c>
-      <c r="M58" s="3">
-        <v>1200</v>
       </c>
       <c r="N58" s="3">
         <v>1200</v>
       </c>
       <c r="O58" s="3">
+        <v>1200</v>
+      </c>
+      <c r="P58" s="3">
         <v>1100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>800</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
@@ -3652,62 +3786,65 @@
       <c r="T58" s="3">
         <v>0</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>4</v>
+      <c r="U58" s="3">
+        <v>0</v>
       </c>
       <c r="V58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W58" s="3">
+      <c r="W58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X58" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E59" s="3">
         <v>1200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3500</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>4</v>
       </c>
@@ -3723,56 +3860,59 @@
       <c r="V59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W59" s="3">
+      <c r="W59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X59" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>17900</v>
+      </c>
+      <c r="E60" s="3">
         <v>22400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>38800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>84900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>68000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>58300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>17100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>19900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>15500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>14200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>26400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>30100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>66500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>49000</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R60" s="3" t="s">
         <v>4</v>
       </c>
@@ -3782,62 +3922,65 @@
       <c r="T60" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U60" s="3">
+      <c r="U60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V60" s="3">
         <v>200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E61" s="3">
         <v>1600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>41500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>39300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>37200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>35100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>33000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>31000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>28900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>51400</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -3856,53 +3999,56 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>8900</v>
+      </c>
+      <c r="E62" s="3">
         <v>9200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>9000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>8000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>7800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>7000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>5300</v>
-      </c>
-      <c r="J62" s="3">
-        <v>5200</v>
       </c>
       <c r="K62" s="3">
         <v>5200</v>
       </c>
       <c r="L62" s="3">
+        <v>5200</v>
+      </c>
+      <c r="M62" s="3">
         <v>5000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>5100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>6000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>69100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>5600</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R62" s="3" t="s">
         <v>4</v>
       </c>
@@ -3912,8 +4058,8 @@
       <c r="T62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U62" s="3">
-        <v>0</v>
+      <c r="U62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V62" s="3">
         <v>0</v>
@@ -3921,8 +4067,11 @@
       <c r="W62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3986,8 +4135,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4051,8 +4203,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4116,53 +4271,56 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>33200</v>
+      </c>
+      <c r="E66" s="3">
         <v>34000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>50400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>95800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>79000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>66900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>64500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>65100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>58600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>54800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>65000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>67300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>164700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>106200</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>4</v>
       </c>
@@ -4172,17 +4330,20 @@
       <c r="T66" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U66" s="3">
+      <c r="U66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V66" s="3">
         <v>200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4206,8 +4367,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4271,8 +4433,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4336,8 +4501,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4378,11 +4546,11 @@
         <v>0</v>
       </c>
       <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
         <v>89000</v>
       </c>
-      <c r="Q70" s="3">
-        <v>0</v>
-      </c>
       <c r="R70" s="3">
         <v>0</v>
       </c>
@@ -4401,8 +4569,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4466,53 +4637,56 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-140000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-142200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-140400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-152100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-150000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-145500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-138500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-111700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-98600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-87300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-75800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-61000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-90100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-55300</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>4</v>
       </c>
@@ -4522,17 +4696,20 @@
       <c r="T72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U72" s="3">
+      <c r="U72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V72" s="3">
         <v>-400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-100</v>
       </c>
-      <c r="W72" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4596,8 +4773,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4661,8 +4841,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4726,53 +4909,56 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>44600</v>
+      </c>
+      <c r="E76" s="3">
         <v>40800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>27600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>12100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>8400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>33500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>44700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>54300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>62800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>75800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>30400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-38200</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>4</v>
       </c>
@@ -4782,17 +4968,20 @@
       <c r="T76" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U76" s="3">
+      <c r="U76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V76" s="3">
         <v>117600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>117900</v>
       </c>
-      <c r="W76" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4856,143 +5045,152 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
     </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>11700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-2200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-4400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-7000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-26800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-13100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-11300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-11500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-14800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>29100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-22200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>6900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-1200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-4500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-1200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-6500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-100</v>
       </c>
-      <c r="W81" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5016,8 +5214,9 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5025,22 +5224,22 @@
         <v>300</v>
       </c>
       <c r="E83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="F83" s="3">
         <v>200</v>
       </c>
       <c r="G83" s="3">
+        <v>200</v>
+      </c>
+      <c r="H83" s="3">
         <v>300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>300</v>
-      </c>
-      <c r="J83" s="3">
-        <v>200</v>
       </c>
       <c r="K83" s="3">
         <v>200</v>
@@ -5055,25 +5254,25 @@
         <v>200</v>
       </c>
       <c r="O83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="P83" s="3">
         <v>100</v>
       </c>
       <c r="Q83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="R83" s="3">
         <v>200</v>
       </c>
       <c r="S83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="T83" s="3">
         <v>100</v>
       </c>
       <c r="U83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V83" s="3">
         <v>0</v>
@@ -5081,8 +5280,11 @@
       <c r="W83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5146,8 +5348,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5211,8 +5416,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5276,8 +5484,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5341,8 +5552,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5406,73 +5620,79 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-9300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>7800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-11300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-7800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-24400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-3200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-6800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-1800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-4700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-400</v>
       </c>
-      <c r="W89" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5496,62 +5716,63 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-400</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
       <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
         <v>-200</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I91" s="3">
+      <c r="I91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J91" s="3">
         <v>-500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-400</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-300</v>
       </c>
       <c r="N91" s="3">
         <v>-300</v>
       </c>
       <c r="O91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="P91" s="3">
         <v>-1300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-100</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
       <c r="U91" s="3">
         <v>0</v>
       </c>
@@ -5561,8 +5782,11 @@
       <c r="W91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5626,8 +5850,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5691,73 +5918,79 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>30100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>2200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-6100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-3500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>1500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-5000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>7700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>15600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>10000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>11200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-41500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-10700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-300</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
-      <c r="V94" s="3" t="s">
-        <v>4</v>
+      <c r="V94" s="3">
+        <v>0</v>
       </c>
       <c r="W94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5781,8 +6014,9 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5825,8 +6059,8 @@
       <c r="P96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -5846,8 +6080,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5911,8 +6148,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5976,8 +6216,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6041,73 +6284,79 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E100" s="3">
         <v>13400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-48500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>10600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-100</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>300</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>3800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>2400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>28600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>16600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>21800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>11500</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
       <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
         <v>117800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6150,8 +6399,8 @@
       <c r="P101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -6171,69 +6420,75 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E102" s="3">
         <v>3900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-16800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>14300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-3200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>2300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-5700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>6100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>4600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>2200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-9500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-38900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>12900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-5800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>9400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>20000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>6600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-100</v>
       </c>
     </row>
